--- a/testakten/familie-amiri-asylfolge-dublin-iv-fluechtlingsanerkennung/xlsx/fluchtroute_und_eurodac.xlsx
+++ b/testakten/familie-amiri-asylfolge-dublin-iv-fluechtlingsanerkennung/xlsx/fluchtroute_und_eurodac.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -502,6 +502,7 @@
     <col width="36" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -512,7 +513,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Testakte: VG Hannover 4 A 4188/26 | Plugin: fachanwalt-migrationsrecht</t>
+          <t>Verfahrensakte VG Hannover 4 A 4188/26</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1174,6 +1175,7 @@
     <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="8" t="inlineStr">
         <is>
@@ -1181,6 +1183,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
